--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roryschram/Documents/Work/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749EE9E9-541D-4942-9827-D1F4D7735913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589EBA55-3593-564D-A027-FEC28990CB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
   </bookViews>
   <sheets>
-    <sheet name="Communication Testing" sheetId="1" r:id="rId1"/>
-    <sheet name="Range Testing" sheetId="2" r:id="rId2"/>
-    <sheet name="Classification Testing" sheetId="3" r:id="rId3"/>
+    <sheet name="USRP Power" sheetId="4" r:id="rId1"/>
+    <sheet name="Communication Testing" sheetId="1" r:id="rId2"/>
+    <sheet name="Range Testing" sheetId="2" r:id="rId3"/>
+    <sheet name="Classification Testing" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.4" hidden="1">'USRP Power'!$D$3</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'USRP Power'!$D$4:$D$21</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'USRP Power'!$G$3</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'USRP Power'!$G$4:$G$21</definedName>
+    <definedName name="_xlchart.v2.0" hidden="1">'USRP Power'!$D$3</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">'USRP Power'!$D$4:$D$21</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">'USRP Power'!$G$3</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">'USRP Power'!$G$4:$G$21</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Small Loopback</t>
   </si>
@@ -50,6 +61,27 @@
   </si>
   <si>
     <t>Attenuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 1 </t>
+  </si>
+  <si>
+    <t>One receive USRP</t>
+  </si>
+  <si>
+    <t>Received dBFS</t>
+  </si>
+  <si>
+    <t>Generated Power dBFS</t>
+  </si>
+  <si>
+    <t>Received dBFS Final</t>
+  </si>
+  <si>
+    <t>received_dBm</t>
+  </si>
+  <si>
+    <t>received_dBFS</t>
   </si>
 </sst>
 </file>
@@ -110,6 +142,1163 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'USRP Power'!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Received dBFS Final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'USRP Power'!$D$4:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>-100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-90</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-85</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-80</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-55</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-45</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-40</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-30</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'USRP Power'!$G$4:$G$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>-100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-98.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-95.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-92.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-87.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-83.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-78.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-72.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-67.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-62.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-57.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-52.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-47.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-43</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-38</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-32.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-27.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8CA4-B14C-9450-C00DF9B63807}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="811439759"/>
+        <c:axId val="811441471"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="811439759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Generated</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" baseline="0"/>
+                  <a:t> Signal Power (dBm)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811441471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="811441471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Received Signal Power (dBFS)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811439759"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>325120</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>86360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>132080</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C9B069E-A2F8-82B0-E352-5BA89C20E4A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,6 +1617,332 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF62291-D714-2E42-A83D-A074856BDF39}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <v>-100</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>-100</v>
+      </c>
+      <c r="G4">
+        <f>F4+E4</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D5">
+        <v>-95</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>-98.6</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G5:G21" si="0">F5+E5</f>
+        <v>-98.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D6">
+        <v>-90</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>-95.8</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D7">
+        <v>-85</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>-92.5</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>-92.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <v>-80</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>-87.9</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>-87.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <v>-75</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>-83.1</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>-83.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <v>-70</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>-78.099999999999994</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>-78.099999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <v>-65</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>-72.5</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>-72.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D12">
+        <v>-60</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>-67.5</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>-55</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>-62.7</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>-62.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D14">
+        <v>-50</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>-57.7</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>-57.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <v>-45</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>-52.8</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>-52.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>-40</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>-47.7</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>-47.7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>-35</v>
+      </c>
+      <c r="E17">
+        <v>40</v>
+      </c>
+      <c r="F17">
+        <v>-83</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>-43</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>-30</v>
+      </c>
+      <c r="E18">
+        <v>40</v>
+      </c>
+      <c r="F18">
+        <v>-78</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>-38</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>-25</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>-72.900000000000006</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>-32.900000000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>-20</v>
+      </c>
+      <c r="E20">
+        <v>40</v>
+      </c>
+      <c r="F20">
+        <v>-67.900000000000006</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>-27.900000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>-15</v>
+      </c>
+      <c r="E21">
+        <v>40</v>
+      </c>
+      <c r="F21">
+        <v>-63</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <f>(E26+9.7768)/0.9524</f>
+        <v>-77.827803443931131</v>
+      </c>
+      <c r="E26">
+        <v>-83.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200B8DD6-86B7-2D45-9650-9EE6C1C0ADA5}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -459,7 +1974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81857181-F8F6-5844-9378-970617983462}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -468,7 +1983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7968BE-0FEC-FD46-A22E-ED18701B82B6}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roryschram/Documents/Work/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589EBA55-3593-564D-A027-FEC28990CB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2BBB20-1E09-C149-991D-96606B1AA031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
   </bookViews>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roryschram/Documents/Work/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2BBB20-1E09-C149-991D-96606B1AA031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB0A2BB-E863-5F4F-B24C-39A3F1B2E73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" activeTab="1" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
   </bookViews>
   <sheets>
     <sheet name="USRP Power" sheetId="4" r:id="rId1"/>
@@ -18,17 +18,7 @@
     <sheet name="Range Testing" sheetId="2" r:id="rId3"/>
     <sheet name="Classification Testing" sheetId="3" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.4" hidden="1">'USRP Power'!$D$3</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'USRP Power'!$D$4:$D$21</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'USRP Power'!$G$3</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'USRP Power'!$G$4:$G$21</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">'USRP Power'!$D$3</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">'USRP Power'!$D$4:$D$21</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">'USRP Power'!$G$3</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">'USRP Power'!$G$4:$G$21</definedName>
-  </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,15 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>Small Loopback</t>
-  </si>
-  <si>
-    <t>Transmit Gain</t>
-  </si>
-  <si>
-    <t>Receive Gain</t>
   </si>
   <si>
     <t>Attenuation</t>
@@ -83,12 +67,51 @@
   <si>
     <t>received_dBFS</t>
   </si>
+  <si>
+    <t>snr_dB_1</t>
+  </si>
+  <si>
+    <t>BER_1</t>
+  </si>
+  <si>
+    <t>snr_dB_2</t>
+  </si>
+  <si>
+    <t>BER_2</t>
+  </si>
+  <si>
+    <t>snr_dB_3</t>
+  </si>
+  <si>
+    <t>BER_3</t>
+  </si>
+  <si>
+    <t>snr_dB_4</t>
+  </si>
+  <si>
+    <t>BER_4</t>
+  </si>
+  <si>
+    <t>snr_dB_5</t>
+  </si>
+  <si>
+    <t>BER_5</t>
+  </si>
+  <si>
+    <t>avg_snr_dB</t>
+  </si>
+  <si>
+    <t>avg_BER</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -101,6 +124,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -497,7 +526,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1629,24 +1658,24 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1921,10 +1950,10 @@
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.2">
@@ -1944,7 +1973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200B8DD6-86B7-2D45-9650-9EE6C1C0ADA5}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
@@ -1953,23 +1982,601 @@
     <col min="4" max="4" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="D3">
+        <v>49.767000000000003</v>
+      </c>
+      <c r="E3">
+        <v>1.4710000000000001</v>
+      </c>
+      <c r="F3">
+        <v>49.744999999999997</v>
+      </c>
+      <c r="G3">
+        <v>1.504</v>
+      </c>
+      <c r="H3">
+        <v>49.57</v>
+      </c>
+      <c r="I3">
+        <v>1.478</v>
+      </c>
+      <c r="J3">
+        <v>49.796999999999997</v>
+      </c>
+      <c r="K3">
+        <v>1.355</v>
+      </c>
+      <c r="L3">
+        <v>49.24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B37">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B48">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B61">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B62">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B63">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B64">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B69">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B70">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B79">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B80">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B81">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B82">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B84">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B86">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B87">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B88">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B94">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B95">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B96">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roryschram/Documents/Work/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB0A2BB-E863-5F4F-B24C-39A3F1B2E73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621EC16A-5D5C-F341-BE4E-84FBB60507E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" activeTab="1" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="Range Testing" sheetId="2" r:id="rId3"/>
     <sheet name="Classification Testing" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="com_testing" localSheetId="1">'Communication Testing'!$A$108:$CW$109</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,8 +41,120 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{ED312627-23C8-CC48-A448-C40A59C9AE17}" name="com_testing" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/roryschram/Documents/Work/masters/com_testing.txt" tab="0" comma="1">
+      <textFields count="101">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="22">
   <si>
     <t>Small Loopback</t>
   </si>
@@ -104,7 +219,7 @@
     <t>avg_BER</t>
   </si>
   <si>
-    <t>test</t>
+    <t>y</t>
   </si>
 </sst>
 </file>
@@ -1330,6 +1445,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="com_testing" connectionId="1" xr16:uid="{882C1BF8-893B-434B-B2B5-FE99D0714097}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1976,10 +2095,89 @@
   <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="59" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="71" max="72" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="95" max="100" width="6.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -2032,53 +2230,11 @@
       <c r="B3">
         <v>100</v>
       </c>
-      <c r="C3">
-        <v>1.4790000000000001</v>
-      </c>
-      <c r="D3">
-        <v>49.767000000000003</v>
-      </c>
-      <c r="E3">
-        <v>1.4710000000000001</v>
-      </c>
-      <c r="F3">
-        <v>49.744999999999997</v>
-      </c>
-      <c r="G3">
-        <v>1.504</v>
-      </c>
-      <c r="H3">
-        <v>49.57</v>
-      </c>
-      <c r="I3">
-        <v>1.478</v>
-      </c>
-      <c r="J3">
-        <v>49.796999999999997</v>
-      </c>
-      <c r="K3">
-        <v>1.355</v>
-      </c>
-      <c r="L3">
-        <v>49.24</v>
-      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>99</v>
       </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5">
@@ -2099,443 +2255,686 @@
       <c r="B8">
         <v>95</v>
       </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>94</v>
       </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>93</v>
       </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>92</v>
       </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>91</v>
       </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>90</v>
       </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>89</v>
       </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>88</v>
       </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>87</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>86</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>85</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>84</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>82</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>81</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>80</v>
       </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>79</v>
       </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>78</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>76</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>75</v>
       </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>74</v>
       </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>73</v>
       </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>72</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>71</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>70</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>69</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>68</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>66</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>65</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>64</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>63</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>62</v>
       </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>61</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>60</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>59</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>58</v>
       </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>57</v>
       </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>56</v>
       </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>55</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49">
         <v>54</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>53</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>52</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>50</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>49</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>48</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56">
         <v>47</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>46</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>45</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>44</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>43</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>42</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>41</v>
       </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C62" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63">
         <v>40</v>
       </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>39</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C64" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>38</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C65" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>37</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>36</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>35</v>
       </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>34</v>
       </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C69" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70">
         <v>33</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C70" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>32</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C71" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>31</v>
       </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>30</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74">
         <v>29</v>
       </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B75">
         <v>28</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C75" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76">
         <v>27</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77">
         <v>26</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C77" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78">
         <v>25</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C78" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79">
         <v>24</v>
       </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C79" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B80">
         <v>23</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C80" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81">
         <v>22</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C81" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>21</v>
       </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C82" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B83">
         <v>20</v>
       </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C83" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B84">
         <v>19</v>
       </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C84" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85">
         <v>18</v>
       </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86">
         <v>17</v>
       </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87">
         <v>16</v>
       </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B88">
         <v>15</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B89">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B90">
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B91">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92">
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93">
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96">
         <v>7</v>
       </c>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roryschram/Documents/Work/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA1CE1E0-8D67-7B41-9640-D8B4684D3BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10D8C1F-463C-B74F-A727-500051681D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" activeTab="2" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" activeTab="3" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
   </bookViews>
   <sheets>
     <sheet name="USRP Power" sheetId="4" r:id="rId1"/>
     <sheet name="Communication Testing" sheetId="1" r:id="rId2"/>
     <sheet name="com_testing_cleaned_up" sheetId="5" r:id="rId3"/>
-    <sheet name="Range Testing" sheetId="2" r:id="rId4"/>
-    <sheet name="Classification Testing" sheetId="3" r:id="rId5"/>
+    <sheet name="com_testing_cleaned_up_snr" sheetId="6" r:id="rId4"/>
+    <sheet name="Range Testing" sheetId="2" r:id="rId5"/>
+    <sheet name="Classification Testing" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Communication Testing'!$CY$3:$CY$88</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Communication Testing'!$CZ$3:$CZ$88</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Communication Testing'!$CY$3:$CY$88</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Communication Testing'!$CZ$3:$CZ$88</definedName>
     <definedName name="com_testing" localSheetId="1">'Communication Testing'!$A$108:$CW$109</definedName>
     <definedName name="com_testing_1" localSheetId="1">'Communication Testing'!$C$3:$CX$88</definedName>
   </definedNames>
@@ -50,7 +47,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{ED312627-23C8-CC48-A448-C40A59C9AE17}" name="com_testing" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/roryschram/Documents/Work/masters/com_testing.txt" tab="0" comma="1">
+    <textPr sourceFile="/Users/roryschram/Documents/Work/masters/com_testing.txt" tab="0" comma="1">
       <textFields count="101">
         <textField/>
         <textField/>
@@ -157,7 +154,7 @@
     </textPr>
   </connection>
   <connection id="2" xr16:uid="{AD20CD6D-62B3-744B-A6C4-A3A456870360}" name="com_testing1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/roryschram/Documents/Work/masters/com_testing.txt" tab="0" comma="1">
+    <textPr sourceFile="/Users/roryschram/Documents/Work/masters/com_testing.txt" tab="0" comma="1">
       <textFields count="100">
         <textField/>
         <textField/>
@@ -266,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="112">
   <si>
     <t>Small Loopback</t>
   </si>
@@ -609,7 +606,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -656,7 +653,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -31819,6 +31816,973 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2101B828-6055-AD4C-B6EB-24947A50444B}">
+  <dimension ref="A1:C87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
+        <v>100</v>
+      </c>
+      <c r="B2" s="2">
+        <v>-42.513599999999997</v>
+      </c>
+      <c r="C2" s="2">
+        <v>49.65908000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>99</v>
+      </c>
+      <c r="B3" s="2">
+        <v>-41.513559999999998</v>
+      </c>
+      <c r="C3" s="2">
+        <v>49.715220000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>98</v>
+      </c>
+      <c r="B4" s="2">
+        <v>-40.51352</v>
+      </c>
+      <c r="C4" s="2">
+        <v>49.610880000000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>97</v>
+      </c>
+      <c r="B5" s="2">
+        <v>-39.513480000000001</v>
+      </c>
+      <c r="C5" s="2">
+        <v>49.58702000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>96</v>
+      </c>
+      <c r="B6" s="2">
+        <v>-38.513440000000003</v>
+      </c>
+      <c r="C6" s="2">
+        <v>49.633319999999983</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>95</v>
+      </c>
+      <c r="B7" s="2">
+        <v>-37.513399999999997</v>
+      </c>
+      <c r="C7" s="2">
+        <v>49.593199999999989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>94</v>
+      </c>
+      <c r="B8" s="2">
+        <v>-36.513359999999999</v>
+      </c>
+      <c r="C8" s="2">
+        <v>49.643240000000013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>93</v>
+      </c>
+      <c r="B9" s="2">
+        <v>-35.51332</v>
+      </c>
+      <c r="C9" s="2">
+        <v>49.609620000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>92</v>
+      </c>
+      <c r="B10" s="2">
+        <v>-34.513280000000002</v>
+      </c>
+      <c r="C10" s="2">
+        <v>49.589780000000019</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>91</v>
+      </c>
+      <c r="B11" s="2">
+        <v>-33.513240000000003</v>
+      </c>
+      <c r="C11" s="2">
+        <v>49.581839999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>90</v>
+      </c>
+      <c r="B12" s="2">
+        <v>-32.513199999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>49.621720000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>89</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-31.513159999999999</v>
+      </c>
+      <c r="C13" s="2">
+        <v>49.642400000000009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>88</v>
+      </c>
+      <c r="B14" s="2">
+        <v>-30.513120000000001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>49.548379999999987</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>87</v>
+      </c>
+      <c r="B15" s="2">
+        <v>-29.513079999999999</v>
+      </c>
+      <c r="C15" s="2">
+        <v>49.544340000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>86</v>
+      </c>
+      <c r="B16" s="2">
+        <v>-28.51304</v>
+      </c>
+      <c r="C16" s="2">
+        <v>49.546540000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2">
+        <v>-27.513000000000002</v>
+      </c>
+      <c r="C17" s="2">
+        <v>49.56333999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>84</v>
+      </c>
+      <c r="B18" s="2">
+        <v>-26.51296</v>
+      </c>
+      <c r="C18" s="2">
+        <v>49.479800000000026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>83</v>
+      </c>
+      <c r="B19" s="2">
+        <v>-25.512920000000001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>49.525299999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>82</v>
+      </c>
+      <c r="B20" s="2">
+        <v>-24.512879999999999</v>
+      </c>
+      <c r="C20" s="2">
+        <v>49.360400000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>81</v>
+      </c>
+      <c r="B21" s="2">
+        <v>-23.512840000000001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>49.355300000000007</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>80</v>
+      </c>
+      <c r="B22" s="2">
+        <v>-22.512799999999999</v>
+      </c>
+      <c r="C22" s="2">
+        <v>49.351439999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>79</v>
+      </c>
+      <c r="B23" s="2">
+        <v>-21.51276</v>
+      </c>
+      <c r="C23" s="2">
+        <v>49.169680000000007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>78</v>
+      </c>
+      <c r="B24" s="2">
+        <v>-20.512720000000002</v>
+      </c>
+      <c r="C24" s="2">
+        <v>49.193100000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>77</v>
+      </c>
+      <c r="B25" s="2">
+        <v>-19.51268</v>
+      </c>
+      <c r="C25" s="2">
+        <v>49.147739999999978</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>76</v>
+      </c>
+      <c r="B26" s="2">
+        <v>-18.512640000000001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>48.995880000000014</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>75</v>
+      </c>
+      <c r="B27" s="2">
+        <v>-17.512599999999999</v>
+      </c>
+      <c r="C27" s="2">
+        <v>48.896260000000012</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>74</v>
+      </c>
+      <c r="B28" s="2">
+        <v>-16.512560000000001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>48.71634000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>73</v>
+      </c>
+      <c r="B29" s="2">
+        <v>-15.51252</v>
+      </c>
+      <c r="C29" s="2">
+        <v>48.515600000000006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>72</v>
+      </c>
+      <c r="B30" s="2">
+        <v>-14.51248</v>
+      </c>
+      <c r="C30" s="2">
+        <v>48.404039999999995</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>71</v>
+      </c>
+      <c r="B31" s="2">
+        <v>-13.51244</v>
+      </c>
+      <c r="C31" s="2">
+        <v>48.255959999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>70</v>
+      </c>
+      <c r="B32" s="2">
+        <v>-12.5124</v>
+      </c>
+      <c r="C32" s="2">
+        <v>47.995100000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>69</v>
+      </c>
+      <c r="B33" s="2">
+        <v>-11.512359999999999</v>
+      </c>
+      <c r="C33" s="2">
+        <v>47.49004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>68</v>
+      </c>
+      <c r="B34" s="2">
+        <v>-10.512320000000001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>47.093919999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>67</v>
+      </c>
+      <c r="B35" s="2">
+        <v>-9.5122800000000005</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46.545199999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>66</v>
+      </c>
+      <c r="B36" s="2">
+        <v>-8.5122400000000003</v>
+      </c>
+      <c r="C36" s="2">
+        <v>45.904360000000018</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>65</v>
+      </c>
+      <c r="B37" s="2">
+        <v>-7.5122</v>
+      </c>
+      <c r="C37" s="2">
+        <v>45.218279999999993</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>64</v>
+      </c>
+      <c r="B38" s="2">
+        <v>-6.5121599999999997</v>
+      </c>
+      <c r="C38" s="2">
+        <v>44.414819999999992</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>63</v>
+      </c>
+      <c r="B39" s="2">
+        <v>-5.5121200000000004</v>
+      </c>
+      <c r="C39" s="2">
+        <v>43.319159999999989</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>62</v>
+      </c>
+      <c r="B40" s="2">
+        <v>-4.5120800000000001</v>
+      </c>
+      <c r="C40" s="2">
+        <v>42.073119999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>61</v>
+      </c>
+      <c r="B41" s="2">
+        <v>-3.5120399999999998</v>
+      </c>
+      <c r="C41" s="2">
+        <v>40.901980000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>60</v>
+      </c>
+      <c r="B42" s="2">
+        <v>-2.512</v>
+      </c>
+      <c r="C42" s="2">
+        <v>39.355720000000012</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>59</v>
+      </c>
+      <c r="B43" s="2">
+        <v>-1.51196</v>
+      </c>
+      <c r="C43" s="2">
+        <v>36.973420000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>58</v>
+      </c>
+      <c r="B44" s="2">
+        <v>-0.51192000000000004</v>
+      </c>
+      <c r="C44" s="2">
+        <v>34.564539999999994</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>57</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.488119999999999</v>
+      </c>
+      <c r="C45" s="2">
+        <v>32.18589999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>56</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1.4881599999999999</v>
+      </c>
+      <c r="C46" s="2">
+        <v>29.225499999999993</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>55</v>
+      </c>
+      <c r="B47" s="2">
+        <v>2.4882</v>
+      </c>
+      <c r="C47" s="2">
+        <v>26.329239999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>54</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3.4882399999999998</v>
+      </c>
+      <c r="C48" s="2">
+        <v>23.413779999999996</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>53</v>
+      </c>
+      <c r="B49" s="2">
+        <v>4.4882799999999996</v>
+      </c>
+      <c r="C49" s="2">
+        <v>20.139580000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>52</v>
+      </c>
+      <c r="B50" s="2">
+        <v>5.4883199999999999</v>
+      </c>
+      <c r="C50" s="2">
+        <v>17.100019999999994</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2">
+        <v>6.4883600000000001</v>
+      </c>
+      <c r="C51" s="2">
+        <v>14.135500000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2">
+        <v>7.4884000000000004</v>
+      </c>
+      <c r="C52" s="2">
+        <v>11.390600000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2">
+        <v>8.4884400000000007</v>
+      </c>
+      <c r="C53" s="2">
+        <v>8.1205000000000016</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>48</v>
+      </c>
+      <c r="B54" s="2">
+        <v>9.4884799999999991</v>
+      </c>
+      <c r="C54" s="2">
+        <v>5.6451200000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>47</v>
+      </c>
+      <c r="B55" s="2">
+        <v>10.488519999999999</v>
+      </c>
+      <c r="C55" s="2">
+        <v>3.8085399999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>46</v>
+      </c>
+      <c r="B56" s="2">
+        <v>11.48856</v>
+      </c>
+      <c r="C56" s="2">
+        <v>2.3219599999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>45</v>
+      </c>
+      <c r="B57" s="2">
+        <v>12.4886</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1.3691199999999994</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>44</v>
+      </c>
+      <c r="B58" s="2">
+        <v>13.48864</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.76959999999999984</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <v>43</v>
+      </c>
+      <c r="B59" s="2">
+        <v>14.48868</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.37186000000000008</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <v>42</v>
+      </c>
+      <c r="B60" s="2">
+        <v>15.488720000000001</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.16643999999999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <v>41</v>
+      </c>
+      <c r="B61" s="2">
+        <v>16.488759999999999</v>
+      </c>
+      <c r="C61" s="2">
+        <v>7.9980000000000009E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <v>40</v>
+      </c>
+      <c r="B62" s="2">
+        <v>17.488800000000001</v>
+      </c>
+      <c r="C62" s="2">
+        <v>4.2900000000000008E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>39</v>
+      </c>
+      <c r="B63" s="2">
+        <v>18.48884</v>
+      </c>
+      <c r="C63" s="2">
+        <v>2.318000000000001E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>38</v>
+      </c>
+      <c r="B64" s="2">
+        <v>19.488880000000002</v>
+      </c>
+      <c r="C64" s="2">
+        <v>2.2179999999999998E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <v>37</v>
+      </c>
+      <c r="B65" s="2">
+        <v>20.48892</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1.1320000000000005E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <v>36</v>
+      </c>
+      <c r="B66" s="2">
+        <v>21.488959999999999</v>
+      </c>
+      <c r="C66" s="2">
+        <v>7.2000000000000041E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>35</v>
+      </c>
+      <c r="B67" s="2">
+        <v>22.489000000000001</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0.50059999999999971</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>34</v>
+      </c>
+      <c r="B68" s="2">
+        <v>23.489039999999999</v>
+      </c>
+      <c r="C68" s="2">
+        <v>4.2400000000000016E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>33</v>
+      </c>
+      <c r="B69" s="2">
+        <v>24.488099999999999</v>
+      </c>
+      <c r="C69" s="2">
+        <v>9.9800000000000028E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>32</v>
+      </c>
+      <c r="B70" s="2">
+        <v>25.499560000000002</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1.3800000000000004E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>31</v>
+      </c>
+      <c r="B71" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1.1600000000000004E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <v>30</v>
+      </c>
+      <c r="B72" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1.1200000000000001E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>29</v>
+      </c>
+      <c r="B73" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="C73" s="2">
+        <v>2.4000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>28</v>
+      </c>
+      <c r="B74" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="C74" s="2">
+        <v>2.4000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>27</v>
+      </c>
+      <c r="B75" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>26</v>
+      </c>
+      <c r="B76" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1.8000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>25</v>
+      </c>
+      <c r="B77" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1.2E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>24</v>
+      </c>
+      <c r="B78" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="C78" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>23</v>
+      </c>
+      <c r="B79" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="C79" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <v>22</v>
+      </c>
+      <c r="B80" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>21</v>
+      </c>
+      <c r="B81" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>20</v>
+      </c>
+      <c r="B82" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="C82" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>19</v>
+      </c>
+      <c r="B83" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="C83" s="2">
+        <v>0.52558000000000005</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>18</v>
+      </c>
+      <c r="B84" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="C84" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>17</v>
+      </c>
+      <c r="B85" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="C85" s="2">
+        <v>0.30326000000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>16</v>
+      </c>
+      <c r="B86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>15</v>
+      </c>
+      <c r="B87" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="C87" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81857181-F8F6-5844-9378-970617983462}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -31827,7 +32791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7968BE-0FEC-FD46-A22E-ED18701B82B6}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roryschram/Documents/Work/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10D8C1F-463C-B74F-A727-500051681D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7590C1CC-1DA9-5C4F-AF0A-712518D22879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16640" activeTab="3" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16600" activeTab="2" xr2:uid="{B2F224B3-2683-8A46-B4CF-646FB0916998}"/>
   </bookViews>
   <sheets>
     <sheet name="USRP Power" sheetId="4" r:id="rId1"/>
@@ -263,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="114">
   <si>
     <t>Small Loopback</t>
   </si>
@@ -600,6 +600,12 @@
   <si>
     <t>BER_50</t>
   </si>
+  <si>
+    <t>avg_snr_dB_computed</t>
+  </si>
+  <si>
+    <t>avg_snr_extrapolated</t>
+  </si>
 </sst>
 </file>
 
@@ -630,12 +636,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -650,11 +662,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1830,11 +1844,11 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="com_testing_1" connectionId="2" xr16:uid="{5D3D6187-659D-DF41-B27C-9622FD93D239}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="com_testing" connectionId="1" xr16:uid="{882C1BF8-893B-434B-B2B5-FE99D0714097}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="com_testing" connectionId="1" xr16:uid="{882C1BF8-893B-434B-B2B5-FE99D0714097}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="com_testing_1" connectionId="2" xr16:uid="{5D3D6187-659D-DF41-B27C-9622FD93D239}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2480,7 +2494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200B8DD6-86B7-2D45-9650-9EE6C1C0ADA5}">
-  <dimension ref="A1:DL103"/>
+  <dimension ref="A1:DL116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -23949,322 +23963,322 @@
       <c r="B68">
         <v>35</v>
       </c>
-      <c r="C68" s="2">
-        <v>22.603999999999999</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="C68" s="4">
+        <v>22.952000000000002</v>
+      </c>
+      <c r="D68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E68" s="4">
+        <v>23.004999999999999</v>
+      </c>
+      <c r="F68" s="4">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E68" s="2">
-        <v>22.571999999999999</v>
-      </c>
-      <c r="F68" s="2">
+      <c r="G68" s="4">
+        <v>22.937999999999999</v>
+      </c>
+      <c r="H68" s="4">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4">
+        <v>23.001000000000001</v>
+      </c>
+      <c r="J68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K68" s="4">
+        <v>22.885999999999999</v>
+      </c>
+      <c r="L68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="M68" s="4">
+        <v>22.954999999999998</v>
+      </c>
+      <c r="N68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O68" s="4">
+        <v>23.018000000000001</v>
+      </c>
+      <c r="P68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>22.940999999999999</v>
+      </c>
+      <c r="R68" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="S68" s="4">
+        <v>22.954000000000001</v>
+      </c>
+      <c r="T68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="U68" s="4">
+        <v>22.98</v>
+      </c>
+      <c r="V68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="W68" s="4">
+        <v>22.968</v>
+      </c>
+      <c r="X68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Y68" s="4">
+        <v>23.03</v>
+      </c>
+      <c r="Z68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AA68" s="4">
+        <v>23.074000000000002</v>
+      </c>
+      <c r="AB68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AC68" s="4">
+        <v>22.928999999999998</v>
+      </c>
+      <c r="AD68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AE68" s="4">
+        <v>22.945</v>
+      </c>
+      <c r="AF68" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="4">
+        <v>22.937000000000001</v>
+      </c>
+      <c r="AH68" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="AI68" s="4">
+        <v>22.971</v>
+      </c>
+      <c r="AJ68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AK68" s="4">
+        <v>22.93</v>
+      </c>
+      <c r="AL68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AM68" s="4">
+        <v>22.988</v>
+      </c>
+      <c r="AN68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AO68" s="4">
+        <v>22.965</v>
+      </c>
+      <c r="AP68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AQ68" s="4">
+        <v>23.003</v>
+      </c>
+      <c r="AR68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AS68" s="4">
+        <v>22.847999999999999</v>
+      </c>
+      <c r="AT68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AU68" s="4">
+        <v>22.971</v>
+      </c>
+      <c r="AV68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AW68" s="4">
+        <v>22.951000000000001</v>
+      </c>
+      <c r="AX68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AY68" s="4">
+        <v>22.995999999999999</v>
+      </c>
+      <c r="AZ68" s="4">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G68" s="2">
-        <v>22.513000000000002</v>
-      </c>
-      <c r="H68" s="2">
+      <c r="BA68" s="4">
+        <v>22.923999999999999</v>
+      </c>
+      <c r="BB68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="BC68" s="4">
+        <v>23.033000000000001</v>
+      </c>
+      <c r="BD68" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="BE68" s="4">
+        <v>23.053000000000001</v>
+      </c>
+      <c r="BF68" s="4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="BG68" s="4">
+        <v>22.837</v>
+      </c>
+      <c r="BH68" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I68" s="2">
-        <v>22.611000000000001</v>
-      </c>
-      <c r="J68" s="2">
+      <c r="BI68" s="4">
+        <v>22.934999999999999</v>
+      </c>
+      <c r="BJ68" s="4">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="K68" s="2">
-        <v>22.501000000000001</v>
-      </c>
-      <c r="L68" s="2">
+      <c r="BK68" s="4">
+        <v>22.971</v>
+      </c>
+      <c r="BL68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="BM68" s="4">
+        <v>22.847999999999999</v>
+      </c>
+      <c r="BN68" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="M68" s="2">
-        <v>22.602</v>
-      </c>
-      <c r="N68" s="2">
+      <c r="BO68" s="4">
+        <v>22.984999999999999</v>
+      </c>
+      <c r="BP68" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="BQ68" s="4">
+        <v>22.957999999999998</v>
+      </c>
+      <c r="BR68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BS68" s="4">
+        <v>23.056000000000001</v>
+      </c>
+      <c r="BT68" s="4">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="O68" s="2">
-        <v>20.376000000000001</v>
-      </c>
-      <c r="P68" s="2">
-        <v>24.779</v>
-      </c>
-      <c r="Q68" s="2">
-        <v>22.587</v>
-      </c>
-      <c r="R68" s="2">
+      <c r="BU68" s="4">
+        <v>22.978000000000002</v>
+      </c>
+      <c r="BV68" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="BW68" s="4">
+        <v>23.061</v>
+      </c>
+      <c r="BX68" s="4">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="S68" s="2">
-        <v>22.670999999999999</v>
-      </c>
-      <c r="T68" s="2">
+      <c r="BY68" s="4">
+        <v>22.907</v>
+      </c>
+      <c r="BZ68" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA68" s="4">
+        <v>22.920999999999999</v>
+      </c>
+      <c r="CB68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="CC68" s="4">
+        <v>22.922000000000001</v>
+      </c>
+      <c r="CD68" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="CE68" s="4">
+        <v>23.047000000000001</v>
+      </c>
+      <c r="CF68" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG68" s="4">
+        <v>23.039000000000001</v>
+      </c>
+      <c r="CH68" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="U68" s="2">
-        <v>22.562999999999999</v>
-      </c>
-      <c r="V68" s="2">
+      <c r="CI68" s="4">
+        <v>22.997</v>
+      </c>
+      <c r="CJ68" s="4">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="W68" s="2">
-        <v>22.599</v>
-      </c>
-      <c r="X68" s="2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="Y68" s="2">
-        <v>22.62</v>
-      </c>
-      <c r="Z68" s="2">
+      <c r="CK68" s="4">
+        <v>23.04</v>
+      </c>
+      <c r="CL68" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="CM68" s="4">
+        <v>22.942</v>
+      </c>
+      <c r="CN68" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AA68" s="2">
-        <v>22.547000000000001</v>
-      </c>
-      <c r="AB68" s="2">
+      <c r="CO68" s="4">
+        <v>22.968</v>
+      </c>
+      <c r="CP68" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="CQ68" s="4">
+        <v>22.963000000000001</v>
+      </c>
+      <c r="CR68" s="4">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="AC68" s="2">
-        <v>22.510999999999999</v>
-      </c>
-      <c r="AD68" s="2">
+      <c r="CS68" s="4">
+        <v>23.029</v>
+      </c>
+      <c r="CT68" s="4">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="AE68" s="2">
-        <v>22.547000000000001</v>
-      </c>
-      <c r="AF68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AG68" s="2">
-        <v>22.571000000000002</v>
-      </c>
-      <c r="AH68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AI68" s="2">
-        <v>22.523</v>
-      </c>
-      <c r="AJ68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AK68" s="2">
-        <v>22.556000000000001</v>
-      </c>
-      <c r="AL68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AM68" s="2">
-        <v>22.634</v>
-      </c>
-      <c r="AN68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="AO68" s="2">
-        <v>22.518999999999998</v>
-      </c>
-      <c r="AP68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="AQ68" s="2">
-        <v>22.545000000000002</v>
-      </c>
-      <c r="AR68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS68" s="2">
-        <v>22.491</v>
-      </c>
-      <c r="AT68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="AU68" s="2">
-        <v>22.635000000000002</v>
-      </c>
-      <c r="AV68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="AW68" s="2">
-        <v>22.497</v>
-      </c>
-      <c r="AX68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY68" s="2">
-        <v>22.555</v>
-      </c>
-      <c r="AZ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA68" s="2">
-        <v>22.483000000000001</v>
-      </c>
-      <c r="BB68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC68" s="2">
-        <v>22.574000000000002</v>
-      </c>
-      <c r="BD68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE68" s="2">
-        <v>22.475000000000001</v>
-      </c>
-      <c r="BF68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="BG68" s="2">
-        <v>22.59</v>
-      </c>
-      <c r="BH68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="BI68" s="2">
-        <v>22.372</v>
-      </c>
-      <c r="BJ68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="BK68" s="2">
-        <v>22.538</v>
-      </c>
-      <c r="BL68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="BM68" s="2">
-        <v>22.53</v>
-      </c>
-      <c r="BN68" s="2">
+      <c r="CU68" s="4">
+        <v>22.956</v>
+      </c>
+      <c r="CV68" s="4">
         <v>0.01</v>
       </c>
-      <c r="BO68" s="2">
-        <v>22.507999999999999</v>
-      </c>
-      <c r="BP68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="BQ68" s="2">
-        <v>22.597000000000001</v>
-      </c>
-      <c r="BR68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="BS68" s="2">
-        <v>22.497</v>
-      </c>
-      <c r="BT68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="BU68" s="2">
-        <v>22.536999999999999</v>
-      </c>
-      <c r="BV68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="BW68" s="2">
-        <v>22.545000000000002</v>
-      </c>
-      <c r="BX68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="BY68" s="2">
-        <v>22.667000000000002</v>
-      </c>
-      <c r="BZ68" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="CA68" s="2">
-        <v>22.495000000000001</v>
-      </c>
-      <c r="CB68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="CC68" s="2">
-        <v>22.501000000000001</v>
-      </c>
-      <c r="CD68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="CE68" s="2">
-        <v>22.567</v>
-      </c>
-      <c r="CF68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG68" s="2">
-        <v>22.518000000000001</v>
-      </c>
-      <c r="CH68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="CI68" s="2">
-        <v>22.516999999999999</v>
-      </c>
-      <c r="CJ68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="CK68" s="2">
-        <v>22.645</v>
-      </c>
-      <c r="CL68" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="CM68" s="2">
-        <v>22.574999999999999</v>
-      </c>
-      <c r="CN68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="CO68" s="2">
-        <v>22.591999999999999</v>
-      </c>
-      <c r="CP68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="CQ68" s="2">
-        <v>22.527999999999999</v>
-      </c>
-      <c r="CR68" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="CS68" s="2">
-        <v>22.588000000000001</v>
-      </c>
-      <c r="CT68" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="CU68" s="2">
-        <v>22.574999999999999</v>
-      </c>
-      <c r="CV68" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="CW68" s="2">
-        <v>22.478999999999999</v>
-      </c>
-      <c r="CX68" s="2">
+      <c r="CW68" s="4">
+        <v>23.001999999999999</v>
+      </c>
+      <c r="CX68" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="CY68" s="2">
         <f t="shared" si="1"/>
-        <v>22.508860000000006</v>
+        <v>22.970159999999996</v>
       </c>
       <c r="CZ68" s="2">
         <f t="shared" ref="CZ68:CZ88" si="2">AVERAGE(D68,F68,H68,J68,L68,N68,P68,R68,T68,V68,X68,Z68,AB68,AD68,AF68,AH68,AJ68,AL68,AN68,AP68,AR68,AT68,AV68,AX68,AZ68,BB68,BD68,BF68,BH68,BJ68,BL68,BN68,BP68,BR68,BT68,BV68,BX68,BZ68,CB68,CD68,CF68,CH68,CJ68,CL68,CN68,CP68,CR68,CT68,CV68,CX68)</f>
-        <v>0.50059999999999971</v>
+        <v>5.4800000000000022E-3</v>
       </c>
       <c r="DJ68" s="3">
         <v>35</v>
       </c>
       <c r="DK68" s="2">
-        <v>22.508860000000006</v>
+        <v>22.970159999999996</v>
       </c>
       <c r="DL68" s="2">
-        <v>0.50059999999999971</v>
+        <v>5.4800000000000022E-3</v>
       </c>
     </row>
     <row r="69" spans="1:116" x14ac:dyDescent="0.2">
@@ -29149,322 +29163,322 @@
       <c r="B84">
         <v>19</v>
       </c>
-      <c r="C84" s="2">
-        <v>37.862000000000002</v>
-      </c>
-      <c r="D84" s="2">
-        <v>0</v>
-      </c>
-      <c r="E84" s="2">
-        <v>37.752000000000002</v>
-      </c>
-      <c r="F84" s="2">
-        <v>0</v>
-      </c>
-      <c r="G84" s="2">
-        <v>37.587000000000003</v>
-      </c>
-      <c r="H84" s="2">
-        <v>0</v>
-      </c>
-      <c r="I84" s="2">
-        <v>37.866999999999997</v>
-      </c>
-      <c r="J84" s="2">
-        <v>0</v>
-      </c>
-      <c r="K84" s="2">
-        <v>37.783999999999999</v>
-      </c>
-      <c r="L84" s="2">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2">
-        <v>37.725999999999999</v>
-      </c>
-      <c r="N84" s="2">
-        <v>0</v>
-      </c>
-      <c r="O84" s="2">
-        <v>37.847000000000001</v>
-      </c>
-      <c r="P84" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="2">
-        <v>37.762999999999998</v>
-      </c>
-      <c r="R84" s="2">
-        <v>0</v>
-      </c>
-      <c r="S84" s="2">
-        <v>37.718000000000004</v>
-      </c>
-      <c r="T84" s="2">
-        <v>0</v>
-      </c>
-      <c r="U84" s="2">
-        <v>37.640999999999998</v>
-      </c>
-      <c r="V84" s="2">
-        <v>0</v>
-      </c>
-      <c r="W84" s="2">
-        <v>37.783000000000001</v>
-      </c>
-      <c r="X84" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="2">
-        <v>37.674999999999997</v>
-      </c>
-      <c r="Z84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="2">
-        <v>37.634</v>
-      </c>
-      <c r="AB84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC84" s="2">
-        <v>37.704999999999998</v>
-      </c>
-      <c r="AD84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE84" s="2">
-        <v>37.71</v>
-      </c>
-      <c r="AF84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG84" s="2">
-        <v>37.738</v>
-      </c>
-      <c r="AH84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI84" s="2">
-        <v>37.968000000000004</v>
-      </c>
-      <c r="AJ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK84" s="2">
-        <v>37.768999999999998</v>
-      </c>
-      <c r="AL84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM84" s="2">
-        <v>37.826999999999998</v>
-      </c>
-      <c r="AN84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO84" s="2">
-        <v>37.715000000000003</v>
-      </c>
-      <c r="AP84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ84" s="2">
-        <v>37.715000000000003</v>
-      </c>
-      <c r="AR84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS84" s="2">
-        <v>37.664000000000001</v>
-      </c>
-      <c r="AT84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU84" s="2">
-        <v>37.814</v>
-      </c>
-      <c r="AV84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW84" s="2">
-        <v>37.631999999999998</v>
-      </c>
-      <c r="AX84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY84" s="2">
-        <v>37.835999999999999</v>
-      </c>
-      <c r="AZ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA84" s="2">
-        <v>37.759</v>
-      </c>
-      <c r="BB84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC84" s="2">
-        <v>37.866999999999997</v>
-      </c>
-      <c r="BD84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE84" s="2">
-        <v>37.718000000000004</v>
-      </c>
-      <c r="BF84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG84" s="2">
-        <v>37.674999999999997</v>
-      </c>
-      <c r="BH84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI84" s="2">
-        <v>37.578000000000003</v>
-      </c>
-      <c r="BJ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK84" s="2">
-        <v>37.64</v>
-      </c>
-      <c r="BL84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM84" s="2">
-        <v>37.603999999999999</v>
-      </c>
-      <c r="BN84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO84" s="2">
-        <v>37.622</v>
-      </c>
-      <c r="BP84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ84" s="2">
-        <v>37.616999999999997</v>
-      </c>
-      <c r="BR84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS84" s="2">
-        <v>37.694000000000003</v>
-      </c>
-      <c r="BT84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU84" s="2">
-        <v>37.825000000000003</v>
-      </c>
-      <c r="BV84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW84" s="2">
-        <v>37.649000000000001</v>
-      </c>
-      <c r="BX84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY84" s="2">
-        <v>37.612000000000002</v>
-      </c>
-      <c r="BZ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA84" s="2">
-        <v>37.659999999999997</v>
-      </c>
-      <c r="CB84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC84" s="2">
-        <v>37.704000000000001</v>
-      </c>
-      <c r="CD84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE84" s="2">
-        <v>37.728000000000002</v>
-      </c>
-      <c r="CF84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG84" s="2">
-        <v>37.673999999999999</v>
-      </c>
-      <c r="CH84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI84" s="2">
-        <v>37.762999999999998</v>
-      </c>
-      <c r="CJ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK84" s="2">
-        <v>35.435000000000002</v>
-      </c>
-      <c r="CL84" s="2">
-        <v>26.279</v>
-      </c>
-      <c r="CM84" s="2">
-        <v>37.834000000000003</v>
-      </c>
-      <c r="CN84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO84" s="2">
-        <v>37.673000000000002</v>
-      </c>
-      <c r="CP84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ84" s="2">
-        <v>37.792000000000002</v>
-      </c>
-      <c r="CR84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS84" s="2">
-        <v>37.741999999999997</v>
-      </c>
-      <c r="CT84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU84" s="2">
-        <v>37.94</v>
-      </c>
-      <c r="CV84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW84" s="2">
-        <v>37.737000000000002</v>
-      </c>
-      <c r="CX84" s="2">
+      <c r="C84" s="4">
+        <v>38.198999999999998</v>
+      </c>
+      <c r="D84" s="4">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4">
+        <v>38.237000000000002</v>
+      </c>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4">
+        <v>38.061999999999998</v>
+      </c>
+      <c r="H84" s="4">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="J84" s="4">
+        <v>0</v>
+      </c>
+      <c r="K84" s="4">
+        <v>38.112000000000002</v>
+      </c>
+      <c r="L84" s="4">
+        <v>0</v>
+      </c>
+      <c r="M84" s="4">
+        <v>38.203000000000003</v>
+      </c>
+      <c r="N84" s="4">
+        <v>0</v>
+      </c>
+      <c r="O84" s="4">
+        <v>38.21</v>
+      </c>
+      <c r="P84" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>38.03</v>
+      </c>
+      <c r="R84" s="4">
+        <v>0</v>
+      </c>
+      <c r="S84" s="4">
+        <v>37.959000000000003</v>
+      </c>
+      <c r="T84" s="4">
+        <v>0</v>
+      </c>
+      <c r="U84" s="4">
+        <v>38.131999999999998</v>
+      </c>
+      <c r="V84" s="4">
+        <v>0</v>
+      </c>
+      <c r="W84" s="4">
+        <v>38.140999999999998</v>
+      </c>
+      <c r="X84" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="4">
+        <v>38.19</v>
+      </c>
+      <c r="Z84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="4">
+        <v>38.253</v>
+      </c>
+      <c r="AB84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="4">
+        <v>38</v>
+      </c>
+      <c r="AD84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="4">
+        <v>38.246000000000002</v>
+      </c>
+      <c r="AF84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="4">
+        <v>38.095999999999997</v>
+      </c>
+      <c r="AH84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="4">
+        <v>38.116</v>
+      </c>
+      <c r="AJ84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="4">
+        <v>38.070999999999998</v>
+      </c>
+      <c r="AL84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="4">
+        <v>38.280999999999999</v>
+      </c>
+      <c r="AN84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="4">
+        <v>38.241999999999997</v>
+      </c>
+      <c r="AP84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="4">
+        <v>38.131</v>
+      </c>
+      <c r="AR84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS84" s="4">
+        <v>38.222999999999999</v>
+      </c>
+      <c r="AT84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU84" s="4">
+        <v>38.164999999999999</v>
+      </c>
+      <c r="AV84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW84" s="4">
+        <v>38.216999999999999</v>
+      </c>
+      <c r="AX84" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY84" s="4">
+        <v>38.076999999999998</v>
+      </c>
+      <c r="AZ84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA84" s="4">
+        <v>38.048000000000002</v>
+      </c>
+      <c r="BB84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC84" s="4">
+        <v>38.091999999999999</v>
+      </c>
+      <c r="BD84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE84" s="4">
+        <v>38.116999999999997</v>
+      </c>
+      <c r="BF84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG84" s="4">
+        <v>38.11</v>
+      </c>
+      <c r="BH84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI84" s="4">
+        <v>38.107999999999997</v>
+      </c>
+      <c r="BJ84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK84" s="4">
+        <v>38.078000000000003</v>
+      </c>
+      <c r="BL84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM84" s="4">
+        <v>38.201999999999998</v>
+      </c>
+      <c r="BN84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO84" s="4">
+        <v>38.279000000000003</v>
+      </c>
+      <c r="BP84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ84" s="4">
+        <v>38.139000000000003</v>
+      </c>
+      <c r="BR84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS84" s="4">
+        <v>38.277999999999999</v>
+      </c>
+      <c r="BT84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU84" s="4">
+        <v>38.130000000000003</v>
+      </c>
+      <c r="BV84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW84" s="4">
+        <v>38.276000000000003</v>
+      </c>
+      <c r="BX84" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY84" s="4">
+        <v>38.137</v>
+      </c>
+      <c r="BZ84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CA84" s="4">
+        <v>38.210999999999999</v>
+      </c>
+      <c r="CB84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC84" s="4">
+        <v>38.069000000000003</v>
+      </c>
+      <c r="CD84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE84" s="4">
+        <v>38.01</v>
+      </c>
+      <c r="CF84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG84" s="4">
+        <v>37.996000000000002</v>
+      </c>
+      <c r="CH84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI84" s="4">
+        <v>38.143999999999998</v>
+      </c>
+      <c r="CJ84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK84" s="4">
+        <v>38.154000000000003</v>
+      </c>
+      <c r="CL84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM84" s="4">
+        <v>38.128</v>
+      </c>
+      <c r="CN84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO84" s="4">
+        <v>38.091999999999999</v>
+      </c>
+      <c r="CP84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ84" s="4">
+        <v>38.158000000000001</v>
+      </c>
+      <c r="CR84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS84" s="4">
+        <v>38.198999999999998</v>
+      </c>
+      <c r="CT84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU84" s="4">
+        <v>38.247999999999998</v>
+      </c>
+      <c r="CV84" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW84" s="4">
+        <v>38.064999999999998</v>
+      </c>
+      <c r="CX84" s="4">
         <v>0</v>
       </c>
       <c r="CY84" s="2">
         <f t="shared" si="3"/>
-        <v>37.685480000000005</v>
+        <v>38.143619999999999</v>
       </c>
       <c r="CZ84" s="2">
         <f t="shared" si="2"/>
-        <v>0.52558000000000005</v>
+        <v>0</v>
       </c>
       <c r="DJ84" s="3">
         <v>19</v>
       </c>
       <c r="DK84" s="2">
-        <v>37.685480000000005</v>
+        <v>38.143619999999999</v>
       </c>
       <c r="DL84" s="2">
-        <v>0.52558000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:116" x14ac:dyDescent="0.2">
@@ -29800,321 +29814,321 @@
         <v>17</v>
       </c>
       <c r="C86" s="2">
-        <v>39.341000000000001</v>
+        <v>39.347000000000001</v>
       </c>
       <c r="D86" s="2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="E86" s="2">
-        <v>39.33</v>
+        <v>40.076999999999998</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
       </c>
       <c r="G86" s="2">
-        <v>39.4</v>
+        <v>39.81</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
       </c>
       <c r="I86" s="2">
-        <v>39.43</v>
+        <v>39.938000000000002</v>
       </c>
       <c r="J86" s="2">
         <v>0</v>
       </c>
       <c r="K86" s="2">
-        <v>39.351999999999997</v>
+        <v>40.015999999999998</v>
       </c>
       <c r="L86" s="2">
         <v>0</v>
       </c>
       <c r="M86" s="2">
-        <v>39.347999999999999</v>
+        <v>39.914000000000001</v>
       </c>
       <c r="N86" s="2">
         <v>0</v>
       </c>
       <c r="O86" s="2">
-        <v>39.456000000000003</v>
+        <v>39.884</v>
       </c>
       <c r="P86" s="2">
         <v>0</v>
       </c>
       <c r="Q86" s="2">
-        <v>39.29</v>
+        <v>40.064</v>
       </c>
       <c r="R86" s="2">
         <v>0</v>
       </c>
       <c r="S86" s="2">
-        <v>39.237000000000002</v>
+        <v>40.085000000000001</v>
       </c>
       <c r="T86" s="2">
         <v>0</v>
       </c>
       <c r="U86" s="2">
-        <v>39.405000000000001</v>
+        <v>39.694000000000003</v>
       </c>
       <c r="V86" s="2">
-        <v>0</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="W86" s="2">
-        <v>39.387</v>
+        <v>39.844000000000001</v>
       </c>
       <c r="X86" s="2">
         <v>0</v>
       </c>
       <c r="Y86" s="2">
-        <v>37.529000000000003</v>
+        <v>39.820999999999998</v>
       </c>
       <c r="Z86" s="2">
-        <v>15.163</v>
+        <v>0</v>
       </c>
       <c r="AA86" s="2">
-        <v>39.360999999999997</v>
+        <v>39.865000000000002</v>
       </c>
       <c r="AB86" s="2">
         <v>0</v>
       </c>
       <c r="AC86" s="2">
-        <v>39.253</v>
+        <v>39.838000000000001</v>
       </c>
       <c r="AD86" s="2">
         <v>0</v>
       </c>
       <c r="AE86" s="2">
-        <v>39.258000000000003</v>
+        <v>39.863999999999997</v>
       </c>
       <c r="AF86" s="2">
         <v>0</v>
       </c>
       <c r="AG86" s="2">
-        <v>39.344999999999999</v>
+        <v>39.832999999999998</v>
       </c>
       <c r="AH86" s="2">
         <v>0</v>
       </c>
       <c r="AI86" s="2">
-        <v>39.518999999999998</v>
+        <v>39.905999999999999</v>
       </c>
       <c r="AJ86" s="2">
         <v>0</v>
       </c>
       <c r="AK86" s="2">
-        <v>39.270000000000003</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="AL86" s="2">
         <v>0</v>
       </c>
       <c r="AM86" s="2">
-        <v>39.262999999999998</v>
+        <v>39.9</v>
       </c>
       <c r="AN86" s="2">
         <v>0</v>
       </c>
       <c r="AO86" s="2">
-        <v>39.317</v>
+        <v>40.078000000000003</v>
       </c>
       <c r="AP86" s="2">
         <v>0</v>
       </c>
       <c r="AQ86" s="2">
-        <v>39.417000000000002</v>
+        <v>40.052999999999997</v>
       </c>
       <c r="AR86" s="2">
         <v>0</v>
       </c>
       <c r="AS86" s="2">
-        <v>39.232999999999997</v>
+        <v>39.859000000000002</v>
       </c>
       <c r="AT86" s="2">
         <v>0</v>
       </c>
       <c r="AU86" s="2">
-        <v>39.362000000000002</v>
+        <v>39.819000000000003</v>
       </c>
       <c r="AV86" s="2">
         <v>0</v>
       </c>
       <c r="AW86" s="2">
-        <v>39.401000000000003</v>
+        <v>39.813000000000002</v>
       </c>
       <c r="AX86" s="2">
         <v>0</v>
       </c>
       <c r="AY86" s="2">
-        <v>39.540999999999997</v>
+        <v>39.923000000000002</v>
       </c>
       <c r="AZ86" s="2">
         <v>0</v>
       </c>
       <c r="BA86" s="2">
-        <v>39.195</v>
+        <v>40</v>
       </c>
       <c r="BB86" s="2">
         <v>0</v>
       </c>
       <c r="BC86" s="2">
-        <v>39.478000000000002</v>
+        <v>39.811999999999998</v>
       </c>
       <c r="BD86" s="2">
         <v>0</v>
       </c>
       <c r="BE86" s="2">
-        <v>39.371000000000002</v>
+        <v>39.744999999999997</v>
       </c>
       <c r="BF86" s="2">
         <v>0</v>
       </c>
       <c r="BG86" s="2">
-        <v>39.564</v>
+        <v>39.878</v>
       </c>
       <c r="BH86" s="2">
         <v>0</v>
       </c>
       <c r="BI86" s="2">
-        <v>39.344999999999999</v>
+        <v>39.807000000000002</v>
       </c>
       <c r="BJ86" s="2">
         <v>0</v>
       </c>
       <c r="BK86" s="2">
-        <v>39.328000000000003</v>
+        <v>39.792999999999999</v>
       </c>
       <c r="BL86" s="2">
         <v>0</v>
       </c>
       <c r="BM86" s="2">
-        <v>39.432000000000002</v>
+        <v>39.856999999999999</v>
       </c>
       <c r="BN86" s="2">
         <v>0</v>
       </c>
       <c r="BO86" s="2">
-        <v>39.249000000000002</v>
+        <v>39.968000000000004</v>
       </c>
       <c r="BP86" s="2">
         <v>0</v>
       </c>
       <c r="BQ86" s="2">
-        <v>39.337000000000003</v>
+        <v>39.802999999999997</v>
       </c>
       <c r="BR86" s="2">
         <v>0</v>
       </c>
       <c r="BS86" s="2">
-        <v>39.271999999999998</v>
+        <v>39.816000000000003</v>
       </c>
       <c r="BT86" s="2">
         <v>0</v>
       </c>
       <c r="BU86" s="2">
-        <v>39.180999999999997</v>
+        <v>40.067999999999998</v>
       </c>
       <c r="BV86" s="2">
         <v>0</v>
       </c>
       <c r="BW86" s="2">
-        <v>39.439</v>
+        <v>40.017000000000003</v>
       </c>
       <c r="BX86" s="2">
         <v>0</v>
       </c>
       <c r="BY86" s="2">
-        <v>39.418999999999997</v>
+        <v>39.122999999999998</v>
       </c>
       <c r="BZ86" s="2">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="CA86" s="2">
-        <v>39.277000000000001</v>
+        <v>39.886000000000003</v>
       </c>
       <c r="CB86" s="2">
         <v>0</v>
       </c>
       <c r="CC86" s="2">
-        <v>39.508000000000003</v>
+        <v>39.776000000000003</v>
       </c>
       <c r="CD86" s="2">
         <v>0</v>
       </c>
       <c r="CE86" s="2">
-        <v>39.332000000000001</v>
+        <v>39.831000000000003</v>
       </c>
       <c r="CF86" s="2">
         <v>0</v>
       </c>
       <c r="CG86" s="2">
-        <v>39.280999999999999</v>
+        <v>39.914999999999999</v>
       </c>
       <c r="CH86" s="2">
         <v>0</v>
       </c>
       <c r="CI86" s="2">
-        <v>39.396000000000001</v>
+        <v>39.841999999999999</v>
       </c>
       <c r="CJ86" s="2">
         <v>0</v>
       </c>
       <c r="CK86" s="2">
-        <v>39.466000000000001</v>
+        <v>39.841000000000001</v>
       </c>
       <c r="CL86" s="2">
         <v>0</v>
       </c>
       <c r="CM86" s="2">
-        <v>39.366999999999997</v>
+        <v>39.984999999999999</v>
       </c>
       <c r="CN86" s="2">
         <v>0</v>
       </c>
       <c r="CO86" s="2">
-        <v>39.246000000000002</v>
+        <v>39.872</v>
       </c>
       <c r="CP86" s="2">
         <v>0</v>
       </c>
       <c r="CQ86" s="2">
-        <v>39.25</v>
+        <v>39.895000000000003</v>
       </c>
       <c r="CR86" s="2">
         <v>0</v>
       </c>
       <c r="CS86" s="2">
-        <v>39.250999999999998</v>
+        <v>39.793999999999997</v>
       </c>
       <c r="CT86" s="2">
         <v>0</v>
       </c>
       <c r="CU86" s="2">
-        <v>39.24</v>
+        <v>39.838999999999999</v>
       </c>
       <c r="CV86" s="2">
         <v>0</v>
       </c>
       <c r="CW86" s="2">
-        <v>39.265999999999998</v>
+        <v>39.770000000000003</v>
       </c>
       <c r="CX86" s="2">
         <v>0</v>
       </c>
       <c r="CY86" s="2">
         <f t="shared" si="3"/>
-        <v>39.310700000000011</v>
+        <v>39.860959999999984</v>
       </c>
       <c r="CZ86" s="2">
         <f t="shared" si="2"/>
-        <v>0.30326000000000003</v>
+        <v>7.486000000000001E-2</v>
       </c>
       <c r="DJ86" s="3">
         <v>17</v>
       </c>
       <c r="DK86" s="2">
-        <v>39.310700000000011</v>
+        <v>39.860959999999984</v>
       </c>
       <c r="DL86" s="2">
-        <v>0.30326000000000003</v>
+        <v>7.486000000000001E-2</v>
       </c>
     </row>
     <row r="87" spans="1:116" x14ac:dyDescent="0.2">
@@ -30840,6 +30854,308 @@
     <row r="103" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B103">
         <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="3:102" x14ac:dyDescent="0.2">
+      <c r="C116">
+        <v>22.952000000000002</v>
+      </c>
+      <c r="D116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E116">
+        <v>23.004999999999999</v>
+      </c>
+      <c r="F116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G116">
+        <v>22.937999999999999</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>23.001000000000001</v>
+      </c>
+      <c r="J116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K116">
+        <v>22.885999999999999</v>
+      </c>
+      <c r="L116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="M116">
+        <v>22.954999999999998</v>
+      </c>
+      <c r="N116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O116">
+        <v>23.018000000000001</v>
+      </c>
+      <c r="P116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q116">
+        <v>22.940999999999999</v>
+      </c>
+      <c r="R116">
+        <v>0.01</v>
+      </c>
+      <c r="S116">
+        <v>22.954000000000001</v>
+      </c>
+      <c r="T116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="U116">
+        <v>22.98</v>
+      </c>
+      <c r="V116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="W116">
+        <v>22.968</v>
+      </c>
+      <c r="X116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Y116">
+        <v>23.03</v>
+      </c>
+      <c r="Z116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AA116">
+        <v>23.074000000000002</v>
+      </c>
+      <c r="AB116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AC116">
+        <v>22.928999999999998</v>
+      </c>
+      <c r="AD116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AE116">
+        <v>22.945</v>
+      </c>
+      <c r="AF116">
+        <v>0</v>
+      </c>
+      <c r="AG116">
+        <v>22.937000000000001</v>
+      </c>
+      <c r="AH116">
+        <v>0.01</v>
+      </c>
+      <c r="AI116">
+        <v>22.971</v>
+      </c>
+      <c r="AJ116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AK116">
+        <v>22.93</v>
+      </c>
+      <c r="AL116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AM116">
+        <v>22.988</v>
+      </c>
+      <c r="AN116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AO116">
+        <v>22.965</v>
+      </c>
+      <c r="AP116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AQ116">
+        <v>23.003</v>
+      </c>
+      <c r="AR116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AS116">
+        <v>22.847999999999999</v>
+      </c>
+      <c r="AT116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AU116">
+        <v>22.971</v>
+      </c>
+      <c r="AV116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AW116">
+        <v>22.951000000000001</v>
+      </c>
+      <c r="AX116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AY116">
+        <v>22.995999999999999</v>
+      </c>
+      <c r="AZ116">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="BA116">
+        <v>22.923999999999999</v>
+      </c>
+      <c r="BB116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="BC116">
+        <v>23.033000000000001</v>
+      </c>
+      <c r="BD116">
+        <v>0.01</v>
+      </c>
+      <c r="BE116">
+        <v>23.053000000000001</v>
+      </c>
+      <c r="BF116">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="BG116">
+        <v>22.837</v>
+      </c>
+      <c r="BH116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BI116">
+        <v>22.934999999999999</v>
+      </c>
+      <c r="BJ116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="BK116">
+        <v>22.971</v>
+      </c>
+      <c r="BL116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="BM116">
+        <v>22.847999999999999</v>
+      </c>
+      <c r="BN116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BO116">
+        <v>22.984999999999999</v>
+      </c>
+      <c r="BP116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="BQ116">
+        <v>22.957999999999998</v>
+      </c>
+      <c r="BR116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BS116">
+        <v>23.056000000000001</v>
+      </c>
+      <c r="BT116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="BU116">
+        <v>22.978000000000002</v>
+      </c>
+      <c r="BV116">
+        <v>0.01</v>
+      </c>
+      <c r="BW116">
+        <v>23.061</v>
+      </c>
+      <c r="BX116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="BY116">
+        <v>22.907</v>
+      </c>
+      <c r="BZ116">
+        <v>0</v>
+      </c>
+      <c r="CA116">
+        <v>22.920999999999999</v>
+      </c>
+      <c r="CB116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="CC116">
+        <v>22.922000000000001</v>
+      </c>
+      <c r="CD116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="CE116">
+        <v>23.047000000000001</v>
+      </c>
+      <c r="CF116">
+        <v>0</v>
+      </c>
+      <c r="CG116">
+        <v>23.039000000000001</v>
+      </c>
+      <c r="CH116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="CI116">
+        <v>22.997</v>
+      </c>
+      <c r="CJ116">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="CK116">
+        <v>23.04</v>
+      </c>
+      <c r="CL116">
+        <v>0.01</v>
+      </c>
+      <c r="CM116">
+        <v>22.942</v>
+      </c>
+      <c r="CN116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="CO116">
+        <v>22.968</v>
+      </c>
+      <c r="CP116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="CQ116">
+        <v>22.963000000000001</v>
+      </c>
+      <c r="CR116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="CS116">
+        <v>23.029</v>
+      </c>
+      <c r="CT116">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="CU116">
+        <v>22.956</v>
+      </c>
+      <c r="CV116">
+        <v>0.01</v>
+      </c>
+      <c r="CW116">
+        <v>23.001999999999999</v>
+      </c>
+      <c r="CX116">
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -30850,21 +31166,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9144942C-2047-734E-9AA5-2B075B56C33F}">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>100</v>
       </c>
@@ -30872,10 +31195,13 @@
         <v>1.52234</v>
       </c>
       <c r="C2" s="2">
+        <v>-42.524340000000201</v>
+      </c>
+      <c r="D2" s="2">
         <v>49.65908000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>99</v>
       </c>
@@ -30883,10 +31209,13 @@
         <v>1.5234399999999997</v>
       </c>
       <c r="C3" s="2">
+        <v>-41.524800000000198</v>
+      </c>
+      <c r="D3" s="2">
         <v>49.715220000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>98</v>
       </c>
@@ -30894,10 +31223,13 @@
         <v>1.5306999999999999</v>
       </c>
       <c r="C4" s="2">
+        <v>-40.525260000000202</v>
+      </c>
+      <c r="D4" s="2">
         <v>49.610880000000009</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>97</v>
       </c>
@@ -30905,10 +31237,13 @@
         <v>1.5457000000000003</v>
       </c>
       <c r="C5" s="2">
+        <v>-39.525720000000199</v>
+      </c>
+      <c r="D5" s="2">
         <v>49.58702000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>96</v>
       </c>
@@ -30916,10 +31251,13 @@
         <v>1.5392800000000002</v>
       </c>
       <c r="C6" s="2">
+        <v>-38.526180000000203</v>
+      </c>
+      <c r="D6" s="2">
         <v>49.633319999999983</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>95</v>
       </c>
@@ -30927,10 +31265,13 @@
         <v>1.5361799999999999</v>
       </c>
       <c r="C7" s="2">
+        <v>-37.526640000000199</v>
+      </c>
+      <c r="D7" s="2">
         <v>49.593199999999989</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>94</v>
       </c>
@@ -30938,10 +31279,13 @@
         <v>1.5522799999999999</v>
       </c>
       <c r="C8" s="2">
+        <v>-36.527100000000203</v>
+      </c>
+      <c r="D8" s="2">
         <v>49.643240000000013</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>93</v>
       </c>
@@ -30949,10 +31293,13 @@
         <v>1.5197000000000003</v>
       </c>
       <c r="C9" s="2">
+        <v>-35.5275600000002</v>
+      </c>
+      <c r="D9" s="2">
         <v>49.609620000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>92</v>
       </c>
@@ -30960,10 +31307,13 @@
         <v>1.5285999999999995</v>
       </c>
       <c r="C10" s="2">
+        <v>-34.528020000000197</v>
+      </c>
+      <c r="D10" s="2">
         <v>49.589780000000019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>91</v>
       </c>
@@ -30971,10 +31321,13 @@
         <v>1.5516199999999998</v>
       </c>
       <c r="C11" s="2">
+        <v>-33.528480000000201</v>
+      </c>
+      <c r="D11" s="2">
         <v>49.581839999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>90</v>
       </c>
@@ -30982,10 +31335,13 @@
         <v>1.54942</v>
       </c>
       <c r="C12" s="2">
+        <v>-32.528940000000198</v>
+      </c>
+      <c r="D12" s="2">
         <v>49.621720000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>89</v>
       </c>
@@ -30993,10 +31349,13 @@
         <v>1.5541399999999999</v>
       </c>
       <c r="C13" s="2">
+        <v>-31.529400000000201</v>
+      </c>
+      <c r="D13" s="2">
         <v>49.642400000000009</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>88</v>
       </c>
@@ -31004,10 +31363,13 @@
         <v>1.5403399999999998</v>
       </c>
       <c r="C14" s="2">
+        <v>-30.529860000000198</v>
+      </c>
+      <c r="D14" s="2">
         <v>49.548379999999987</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>87</v>
       </c>
@@ -31015,10 +31377,13 @@
         <v>1.54504</v>
       </c>
       <c r="C15" s="2">
+        <v>-29.530320000000199</v>
+      </c>
+      <c r="D15" s="2">
         <v>49.544340000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>86</v>
       </c>
@@ -31026,10 +31391,13 @@
         <v>1.5403000000000002</v>
       </c>
       <c r="C16" s="2">
+        <v>-28.530780000000199</v>
+      </c>
+      <c r="D16" s="2">
         <v>49.546540000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>85</v>
       </c>
@@ -31037,10 +31405,13 @@
         <v>1.53928</v>
       </c>
       <c r="C17" s="2">
+        <v>-27.531240000000199</v>
+      </c>
+      <c r="D17" s="2">
         <v>49.56333999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>84</v>
       </c>
@@ -31048,10 +31419,13 @@
         <v>1.5539000000000001</v>
       </c>
       <c r="C18" s="2">
+        <v>-26.5317000000002</v>
+      </c>
+      <c r="D18" s="2">
         <v>49.479800000000026</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>83</v>
       </c>
@@ -31059,10 +31433,13 @@
         <v>1.5248199999999996</v>
       </c>
       <c r="C19" s="2">
+        <v>-25.5321600000002</v>
+      </c>
+      <c r="D19" s="2">
         <v>49.525299999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>82</v>
       </c>
@@ -31070,10 +31447,13 @@
         <v>1.5626800000000003</v>
       </c>
       <c r="C20" s="2">
+        <v>-24.5326200000002</v>
+      </c>
+      <c r="D20" s="2">
         <v>49.360400000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>81</v>
       </c>
@@ -31081,10 +31461,13 @@
         <v>1.56386</v>
       </c>
       <c r="C21" s="2">
+        <v>-23.533080000000201</v>
+      </c>
+      <c r="D21" s="2">
         <v>49.355300000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>80</v>
       </c>
@@ -31092,10 +31475,13 @@
         <v>1.5668600000000001</v>
       </c>
       <c r="C22" s="2">
+        <v>-22.533540000000201</v>
+      </c>
+      <c r="D22" s="2">
         <v>49.351439999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>79</v>
       </c>
@@ -31103,10 +31489,13 @@
         <v>1.5707599999999999</v>
       </c>
       <c r="C23" s="2">
+        <v>-21.534000000000201</v>
+      </c>
+      <c r="D23" s="2">
         <v>49.169680000000007</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>78</v>
       </c>
@@ -31114,10 +31503,13 @@
         <v>1.5955200000000007</v>
       </c>
       <c r="C24" s="2">
+        <v>-20.534460000000202</v>
+      </c>
+      <c r="D24" s="2">
         <v>49.193100000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>77</v>
       </c>
@@ -31125,10 +31517,13 @@
         <v>1.5895199999999996</v>
       </c>
       <c r="C25" s="2">
+        <v>-19.534920000000199</v>
+      </c>
+      <c r="D25" s="2">
         <v>49.147739999999978</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>76</v>
       </c>
@@ -31136,10 +31531,13 @@
         <v>1.5997199999999998</v>
       </c>
       <c r="C26" s="2">
+        <v>-18.535380000000199</v>
+      </c>
+      <c r="D26" s="2">
         <v>48.995880000000014</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>75</v>
       </c>
@@ -31147,10 +31545,13 @@
         <v>1.6084200000000006</v>
       </c>
       <c r="C27" s="2">
+        <v>-17.5358400000001</v>
+      </c>
+      <c r="D27" s="2">
         <v>48.896260000000012</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>74</v>
       </c>
@@ -31158,10 +31559,13 @@
         <v>1.6378400000000004</v>
       </c>
       <c r="C28" s="2">
+        <v>-16.5363000000001</v>
+      </c>
+      <c r="D28" s="2">
         <v>48.71634000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>73</v>
       </c>
@@ -31169,10 +31573,13 @@
         <v>1.6349600000000002</v>
       </c>
       <c r="C29" s="2">
+        <v>-15.5367600000001</v>
+      </c>
+      <c r="D29" s="2">
         <v>48.515600000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>72</v>
       </c>
@@ -31180,10 +31587,13 @@
         <v>1.66428</v>
       </c>
       <c r="C30" s="2">
+        <v>-14.537220000000101</v>
+      </c>
+      <c r="D30" s="2">
         <v>48.404039999999995</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>71</v>
       </c>
@@ -31191,10 +31601,13 @@
         <v>1.6821800000000005</v>
       </c>
       <c r="C31" s="2">
+        <v>-13.537680000000099</v>
+      </c>
+      <c r="D31" s="2">
         <v>48.255959999999995</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>70</v>
       </c>
@@ -31202,10 +31615,13 @@
         <v>1.6994000000000002</v>
       </c>
       <c r="C32" s="2">
+        <v>-12.5381400000001</v>
+      </c>
+      <c r="D32" s="2">
         <v>47.995100000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>69</v>
       </c>
@@ -31213,10 +31629,13 @@
         <v>1.7350999999999996</v>
       </c>
       <c r="C33" s="2">
+        <v>-11.5386000000001</v>
+      </c>
+      <c r="D33" s="2">
         <v>47.49004</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>68</v>
       </c>
@@ -31224,10 +31643,13 @@
         <v>1.7811599999999999</v>
       </c>
       <c r="C34" s="2">
+        <v>-10.5390600000001</v>
+      </c>
+      <c r="D34" s="2">
         <v>47.093919999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>67</v>
       </c>
@@ -31235,10 +31657,13 @@
         <v>1.8313400000000002</v>
       </c>
       <c r="C35" s="2">
+        <v>-9.5395200000001008</v>
+      </c>
+      <c r="D35" s="2">
         <v>46.545199999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>66</v>
       </c>
@@ -31246,10 +31671,13 @@
         <v>1.9032400000000005</v>
       </c>
       <c r="C36" s="2">
+        <v>-8.5399800000000994</v>
+      </c>
+      <c r="D36" s="2">
         <v>45.904360000000018</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>65</v>
       </c>
@@ -31257,10 +31685,13 @@
         <v>1.98576</v>
       </c>
       <c r="C37" s="2">
+        <v>-7.5404400000000997</v>
+      </c>
+      <c r="D37" s="2">
         <v>45.218279999999993</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>64</v>
       </c>
@@ -31268,10 +31699,13 @@
         <v>2.0678200000000002</v>
       </c>
       <c r="C38" s="2">
+        <v>-6.5409000000001001</v>
+      </c>
+      <c r="D38" s="2">
         <v>44.414819999999992</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>63</v>
       </c>
@@ -31279,10 +31713,13 @@
         <v>2.2001399999999998</v>
       </c>
       <c r="C39" s="2">
+        <v>-5.5413600000001004</v>
+      </c>
+      <c r="D39" s="2">
         <v>43.319159999999989</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>62</v>
       </c>
@@ -31290,10 +31727,13 @@
         <v>2.3091800000000005</v>
       </c>
       <c r="C40" s="2">
+        <v>-4.5418200000000999</v>
+      </c>
+      <c r="D40" s="2">
         <v>42.073119999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>61</v>
       </c>
@@ -31301,10 +31741,13 @@
         <v>2.4543600000000008</v>
       </c>
       <c r="C41" s="2">
+        <v>-3.5422800000000998</v>
+      </c>
+      <c r="D41" s="2">
         <v>40.901980000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>60</v>
       </c>
@@ -31312,10 +31755,13 @@
         <v>2.6227199999999997</v>
       </c>
       <c r="C42" s="2">
+        <v>-2.5427400000001001</v>
+      </c>
+      <c r="D42" s="2">
         <v>39.355720000000012</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>59</v>
       </c>
@@ -31323,10 +31769,13 @@
         <v>2.9076999999999997</v>
       </c>
       <c r="C43" s="2">
+        <v>-1.5432000000001</v>
+      </c>
+      <c r="D43" s="2">
         <v>36.973420000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>58</v>
       </c>
@@ -31334,10 +31783,13 @@
         <v>3.2399800000000005</v>
       </c>
       <c r="C44" s="2">
+        <v>-0.54366000000009895</v>
+      </c>
+      <c r="D44" s="2">
         <v>34.564539999999994</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>57</v>
       </c>
@@ -31345,10 +31797,13 @@
         <v>3.5830599999999992</v>
       </c>
       <c r="C45" s="2">
+        <v>0.45587999999990098</v>
+      </c>
+      <c r="D45" s="2">
         <v>32.18589999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>56</v>
       </c>
@@ -31356,10 +31811,13 @@
         <v>4.0114200000000002</v>
       </c>
       <c r="C46" s="2">
+        <v>1.4554199999999</v>
+      </c>
+      <c r="D46" s="2">
         <v>29.225499999999993</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>55</v>
       </c>
@@ -31367,10 +31825,13 @@
         <v>4.4713799999999999</v>
       </c>
       <c r="C47" s="2">
+        <v>2.4549599999998999</v>
+      </c>
+      <c r="D47" s="2">
         <v>26.329239999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>54</v>
       </c>
@@ -31378,10 +31839,13 @@
         <v>4.9668800000000006</v>
       </c>
       <c r="C48" s="2">
+        <v>3.4544999999999</v>
+      </c>
+      <c r="D48" s="2">
         <v>23.413779999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>53</v>
       </c>
@@ -31389,10 +31853,13 @@
         <v>5.6290400000000007</v>
       </c>
       <c r="C49" s="2">
+        <v>4.4540399999998996</v>
+      </c>
+      <c r="D49" s="2">
         <v>20.139580000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>52</v>
       </c>
@@ -31400,10 +31867,13 @@
         <v>6.3315600000000005</v>
       </c>
       <c r="C50" s="2">
+        <v>5.4535799999999002</v>
+      </c>
+      <c r="D50" s="2">
         <v>17.100019999999994</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>51</v>
       </c>
@@ -31411,10 +31881,13 @@
         <v>7.0576799999999995</v>
       </c>
       <c r="C51" s="2">
+        <v>6.4531199999998998</v>
+      </c>
+      <c r="D51" s="2">
         <v>14.135500000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -31422,10 +31895,13 @@
         <v>7.8236400000000001</v>
       </c>
       <c r="C52" s="2">
+        <v>7.4526599999999004</v>
+      </c>
+      <c r="D52" s="2">
         <v>11.390600000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>49</v>
       </c>
@@ -31433,10 +31909,13 @@
         <v>8.8960400000000011</v>
       </c>
       <c r="C53" s="2">
+        <v>8.4521999999999</v>
+      </c>
+      <c r="D53" s="2">
         <v>8.1205000000000016</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>48</v>
       </c>
@@ -31444,10 +31923,13 @@
         <v>9.9086800000000022</v>
       </c>
       <c r="C54" s="2">
+        <v>9.4517399999998997</v>
+      </c>
+      <c r="D54" s="2">
         <v>5.6451200000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>47</v>
       </c>
@@ -31455,10 +31937,13 @@
         <v>10.85482</v>
       </c>
       <c r="C55" s="2">
+        <v>10.451279999999899</v>
+      </c>
+      <c r="D55" s="2">
         <v>3.8085399999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>46</v>
       </c>
@@ -31466,10 +31951,13 @@
         <v>11.862060000000001</v>
       </c>
       <c r="C56" s="2">
+        <v>11.450819999999901</v>
+      </c>
+      <c r="D56" s="2">
         <v>2.3219599999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>45</v>
       </c>
@@ -31477,10 +31965,13 @@
         <v>12.783099999999999</v>
       </c>
       <c r="C57" s="2">
+        <v>12.4503599999999</v>
+      </c>
+      <c r="D57" s="2">
         <v>1.3691199999999994</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>44</v>
       </c>
@@ -31488,10 +31979,13 @@
         <v>13.676799999999998</v>
       </c>
       <c r="C58" s="2">
+        <v>13.4499</v>
+      </c>
+      <c r="D58" s="2">
         <v>0.76959999999999984</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>43</v>
       </c>
@@ -31499,10 +31993,13 @@
         <v>14.685359999999998</v>
       </c>
       <c r="C59" s="2">
+        <v>14.449439999999999</v>
+      </c>
+      <c r="D59" s="2">
         <v>0.37186000000000008</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>42</v>
       </c>
@@ -31510,10 +32007,13 @@
         <v>15.687080000000002</v>
       </c>
       <c r="C60" s="2">
+        <v>15.448980000000001</v>
+      </c>
+      <c r="D60" s="2">
         <v>0.16643999999999995</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>41</v>
       </c>
@@ -31521,10 +32021,13 @@
         <v>16.627400000000002</v>
       </c>
       <c r="C61" s="2">
+        <v>16.448519999999998</v>
+      </c>
+      <c r="D61" s="2">
         <v>7.9980000000000009E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>40</v>
       </c>
@@ -31532,10 +32035,13 @@
         <v>17.581179999999996</v>
       </c>
       <c r="C62" s="2">
+        <v>17.448060000000002</v>
+      </c>
+      <c r="D62" s="2">
         <v>4.2900000000000008E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>39</v>
       </c>
@@ -31543,10 +32049,13 @@
         <v>18.561160000000001</v>
       </c>
       <c r="C63" s="2">
+        <v>18.447600000000001</v>
+      </c>
+      <c r="D63" s="2">
         <v>2.318000000000001E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>38</v>
       </c>
@@ -31554,10 +32063,13 @@
         <v>19.605679999999996</v>
       </c>
       <c r="C64" s="2">
+        <v>19.447140000000001</v>
+      </c>
+      <c r="D64" s="2">
         <v>2.2179999999999998E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -31565,10 +32077,13 @@
         <v>20.593739999999997</v>
       </c>
       <c r="C65" s="2">
+        <v>20.446680000000001</v>
+      </c>
+      <c r="D65" s="2">
         <v>1.1320000000000005E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>36</v>
       </c>
@@ -31576,21 +32091,27 @@
         <v>21.645160000000001</v>
       </c>
       <c r="C66" s="2">
+        <v>21.44622</v>
+      </c>
+      <c r="D66" s="2">
         <v>7.2000000000000041E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>35</v>
       </c>
       <c r="B67" s="2">
-        <v>22.508860000000006</v>
+        <v>22.970159999999996</v>
       </c>
       <c r="C67" s="2">
-        <v>0.50059999999999971</v>
+        <v>22.44576</v>
+      </c>
+      <c r="D67" s="2">
+        <v>5.4800000000000022E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>34</v>
       </c>
@@ -31598,10 +32119,13 @@
         <v>23.489039999999999</v>
       </c>
       <c r="C68" s="2">
+        <v>23.4453</v>
+      </c>
+      <c r="D68" s="2">
         <v>4.2400000000000016E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>33</v>
       </c>
@@ -31609,10 +32133,13 @@
         <v>24.488099999999999</v>
       </c>
       <c r="C69" s="2">
+        <v>24.444839999999999</v>
+      </c>
+      <c r="D69" s="2">
         <v>9.9800000000000028E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>32</v>
       </c>
@@ -31620,10 +32147,13 @@
         <v>25.499560000000002</v>
       </c>
       <c r="C70" s="2">
+        <v>25.444379999999999</v>
+      </c>
+      <c r="D70" s="2">
         <v>1.3800000000000004E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>31</v>
       </c>
@@ -31631,10 +32161,13 @@
         <v>26.421700000000008</v>
       </c>
       <c r="C71" s="2">
+        <v>26.443919999999999</v>
+      </c>
+      <c r="D71" s="2">
         <v>1.1600000000000004E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>30</v>
       </c>
@@ -31642,10 +32175,13 @@
         <v>27.348300000000005</v>
       </c>
       <c r="C72" s="2">
+        <v>27.443460000000002</v>
+      </c>
+      <c r="D72" s="2">
         <v>1.1200000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>29</v>
       </c>
@@ -31653,10 +32189,13 @@
         <v>28.422260000000001</v>
       </c>
       <c r="C73" s="2">
+        <v>28.443000000000001</v>
+      </c>
+      <c r="D73" s="2">
         <v>2.4000000000000001E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>28</v>
       </c>
@@ -31664,21 +32203,27 @@
         <v>29.442540000000005</v>
       </c>
       <c r="C74" s="2">
+        <v>29.442540000000005</v>
+      </c>
+      <c r="D74" s="2">
         <v>2.4000000000000001E-4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>27</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="5">
         <v>30.379360000000005</v>
       </c>
       <c r="C75" s="2">
+        <v>30.379360000000005</v>
+      </c>
+      <c r="D75" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>26</v>
       </c>
@@ -31686,10 +32231,13 @@
         <v>31.378499999999999</v>
       </c>
       <c r="C76" s="2">
+        <v>31.379000000000001</v>
+      </c>
+      <c r="D76" s="2">
         <v>1.8000000000000001E-4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>25</v>
       </c>
@@ -31697,10 +32245,13 @@
         <v>32.283080000000012</v>
       </c>
       <c r="C77" s="2">
+        <v>32.378639999999997</v>
+      </c>
+      <c r="D77" s="2">
         <v>1.2E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>24</v>
       </c>
@@ -31708,10 +32259,13 @@
         <v>33.186999999999991</v>
       </c>
       <c r="C78" s="2">
+        <v>33.378279999999997</v>
+      </c>
+      <c r="D78" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>23</v>
       </c>
@@ -31719,10 +32273,13 @@
         <v>34.125340000000001</v>
       </c>
       <c r="C79" s="2">
+        <v>34.377920000000003</v>
+      </c>
+      <c r="D79" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>22</v>
       </c>
@@ -31730,10 +32287,13 @@
         <v>35.021959999999993</v>
       </c>
       <c r="C80" s="2">
+        <v>35.377560000000003</v>
+      </c>
+      <c r="D80" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>21</v>
       </c>
@@ -31741,10 +32301,13 @@
         <v>35.868079999999999</v>
       </c>
       <c r="C81" s="2">
+        <v>36.377200000000002</v>
+      </c>
+      <c r="D81" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>20</v>
       </c>
@@ -31752,21 +32315,27 @@
         <v>36.68186</v>
       </c>
       <c r="C82" s="2">
+        <v>37.376840000000001</v>
+      </c>
+      <c r="D82" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>19</v>
       </c>
       <c r="B83" s="2">
-        <v>37.685480000000005</v>
+        <v>38.143619999999999</v>
       </c>
       <c r="C83" s="2">
-        <v>0.52558000000000005</v>
+        <v>38.376480000000001</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>18</v>
       </c>
@@ -31774,21 +32343,27 @@
         <v>38.583879999999994</v>
       </c>
       <c r="C84" s="2">
+        <v>39.37612</v>
+      </c>
+      <c r="D84" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>17</v>
       </c>
       <c r="B85" s="2">
-        <v>39.310700000000011</v>
+        <v>39.860959999999984</v>
       </c>
       <c r="C85" s="2">
-        <v>0.30326000000000003</v>
+        <v>40.37576</v>
+      </c>
+      <c r="D85" s="2">
+        <v>7.486000000000001E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>16</v>
       </c>
@@ -31796,10 +32371,13 @@
         <v>40.051859999999998</v>
       </c>
       <c r="C86" s="2">
+        <v>41.375399999999999</v>
+      </c>
+      <c r="D86" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>15</v>
       </c>
@@ -31807,11 +32385,15 @@
         <v>40.749720000000003</v>
       </c>
       <c r="C87" s="2">
+        <v>42.375039999999998</v>
+      </c>
+      <c r="D87" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
